--- a/registration_forms/046_trade_show_check_in_form--registration_forms.xlsx
+++ b/registration_forms/046_trade_show_check_in_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>checkin_user</t>
+          <t>checkin_user_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Checkin User</t>
+          <t>Checkin User 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>checkin_time</t>
+          <t>checkin_time_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Checkin Time</t>
+          <t>Checkin Time 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>checkin_status</t>
+          <t>checkin_status_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Checkin Status</t>
+          <t>Checkin Status 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>event_id_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Event Id 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>checkin_location</t>
+          <t>checkin_location_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Checkin Location</t>
+          <t>Checkin Location 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>assigned_tool_other</t>
+          <t>assigned_tool_other_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other Tool</t>
+          <t>Assigned Tool Other 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'checked_in',_'label':_'checked_in'}</t>
+          <t>checked_in</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'checked_in', 'label': 'Checked In'}</t>
+          <t>Checked In</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'not_checked_in',_'label':_'not_checked_in'}</t>
+          <t>not_checked_in</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'not_checked_in', 'label': 'Not Checked In'}</t>
+          <t>Not Checked In</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'user1',_'label':_'user1'}</t>
+          <t>user1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'user1', 'label': 'user1'}</t>
+          <t>user1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'user2',_'label':_'user2'}</t>
+          <t>user2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'user2', 'label': 'user2'}</t>
+          <t>user2</t>
         </is>
       </c>
     </row>
@@ -1250,114 +1250,114 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'user3',_'label':_'user3'}</t>
+          <t>user3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'user3', 'label': 'user3'}</t>
+          <t>user3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>checkin_user_choices</t>
+          <t>checkin_user_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'user1',_'label':_'user1'}</t>
+          <t>user1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'user1', 'label': 'user1'}</t>
+          <t>user1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>checkin_user_choices</t>
+          <t>checkin_user_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'user2',_'label':_'user2'}</t>
+          <t>user2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'user2', 'label': 'user2'}</t>
+          <t>user2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>checkin_user_choices</t>
+          <t>checkin_user_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'user3',_'label':_'user3'}</t>
+          <t>user3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'user3', 'label': 'user3'}</t>
+          <t>user3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>checkin_status_choices</t>
+          <t>checkin_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'checked_in',_'label':_'checked_in'}</t>
+          <t>checked_in</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'checked_in', 'label': 'Checked In'}</t>
+          <t>Checked In</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>checkin_status_choices</t>
+          <t>checkin_status_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'not_checked_in',_'label':_'not_checked_in'}</t>
+          <t>not_checked_in</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'not_checked_in', 'label': 'Not Checked In'}</t>
+          <t>Not Checked In</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>checkin_status_choices</t>
+          <t>checkin_status_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
